--- a/study/question_windows.xlsx
+++ b/study/question_windows.xlsx
@@ -4510,22 +4510,22 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>21</v>
+        <v>12.3</v>
       </c>
       <c r="F105" t="n">
-        <v>25.9</v>
+        <v>15.2</v>
       </c>
       <c r="G105" t="n">
         <v>1</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>La donna del negozio di cappelli La vide e subito sbadigliò anche lei</t>
+          <t>La sorellina era stanca e sbadigliò</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>La donna del negozio di cappelli La vide e subito sbadigliò anche lei</t>
+          <t>La sorellina era stanca e sbadigliò</t>
         </is>
       </c>
     </row>
@@ -4549,22 +4549,22 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>21.1</v>
+        <v>12.3</v>
       </c>
       <c r="F106" t="n">
-        <v>26</v>
+        <v>15.2</v>
       </c>
       <c r="G106" t="n">
         <v>1</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>La donna del negozio di cappelli La vide e subito sbadigliò anche lei</t>
+          <t>La sorellina era stanca e sbadigliò</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>La donna del negozio di cappelli La vide e subito sbadigliò anche lei</t>
+          <t>La sorellina era stanca e sbadigliò</t>
         </is>
       </c>
     </row>
@@ -4588,22 +4588,22 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>12.3</v>
+        <v>21</v>
       </c>
       <c r="F107" t="n">
-        <v>15.2</v>
+        <v>25.9</v>
       </c>
       <c r="G107" t="n">
         <v>1</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>La sorellina era stanca e sbadigliò</t>
+          <t>La donna del negozio di cappelli La vide e subito sbadigliò anche lei</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>La sorellina era stanca e sbadigliò</t>
+          <t>La donna del negozio di cappelli La vide e subito sbadigliò anche lei</t>
         </is>
       </c>
     </row>
@@ -4627,22 +4627,22 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>12.3</v>
+        <v>21.1</v>
       </c>
       <c r="F108" t="n">
-        <v>15.2</v>
+        <v>26</v>
       </c>
       <c r="G108" t="n">
         <v>1</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>La sorellina era stanca e sbadigliò</t>
+          <t>La donna del negozio di cappelli La vide e subito sbadigliò anche lei</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>La sorellina era stanca e sbadigliò</t>
+          <t>La donna del negozio di cappelli La vide e subito sbadigliò anche lei</t>
         </is>
       </c>
     </row>
